--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-referral-servicerequest-diagnosticimaging</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-referral-servicerequest-diagnosticimaging</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}ereferral-inv-subject-contained:The subject must reference a Patient as contained. {subject.reference.startsWith('#')}ereferral-inv-supportingInfo-safetyChecklist-contained:supportingInfo[safetyChecklist] must reference the contained safety checklist. {supportingInfo.reference.where($this.startsWith('#')).select(substring(1)).all($this in %resource.contained.where(meta.profile contains 'https://www.riziv-inami.be/standards/fhir/ereferral/StructureDefinition/ereferral-imaging-attention-conditions-response').id)}ereferral-inv-status-reason-text-pseudonymized:When statusReason text is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'http://hl7.org/fhir/StructureDefinition/request-statusReason').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-urgent-requires-urgency-justification:The urgencyJustification extension must be present when priority is urgent. {priority != 'urgent' or extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification').exists()}ereferral-inv-urgency-justification-value-pseudonymized:When urgencyJustification.valueString is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification').value.ofType(string).all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-concept-text-pseudonymized:When patientCondition concept text is present, it must have the be-ext-pseudonymization extension. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-code-or-text:patientCondition must contain either a coded indication from the allowed ValueSet or encrypted free text. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all(coding.exists() or text.exists())}ereferral-inv-contained-patient-birthdate-encrypted:The birthDate of the contained Patient must not be sent in clear text and must be represented only by the encrypted be-ext-pseudonymized-content extension. {contained.ofType(Patient).all(birthDate.hasValue().not() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists())}ereferral-inv-contained-patient-gender-at-birth-encrypted:The contained Patient genderAtBirth must always be coded as 'other' and must be accompanied by the be-ext-pseudonymized-content encryption extension. {contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').all(value.ofType(CodeableConcept).coding.where(system = 'http://hl7.org/fhir/administrative-gender' and code = 'other').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists()) and contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}ereferral-inv-subject-contained:The subject must reference a Patient as contained. {subject.reference.startsWith('#')}ereferral-inv-supportingInfo-safetyChecklist-contained:supportingInfo[safetyChecklist] must reference the contained safety checklist. {supportingInfo.reference.where($this.startsWith('#')).select(substring(1)).all($this in %resource.contained.where(meta.profile contains 'https://www.riziv-inami.be/standards/fhir/ereferral/StructureDefinition/ereferral-imaging-attention-conditions-response').id)}ereferral-inv-status-reason-text-pseudonymized:When statusReason text is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'http://hl7.org/fhir/StructureDefinition/request-statusReason').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-urgent-requires-urgency-justification:The urgencyJustification extension must be present when priority is urgent. {priority != 'urgent' or extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification').exists()}ereferral-inv-urgency-justification-value-pseudonymized:When urgencyJustification.valueString is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification').value.ofType(string).all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-concept-text-pseudonymized:When patientCondition concept text is present, it must have the be-ext-pseudonymization extension. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-code-or-text:patientCondition must contain either a coded indication from the allowed ValueSet or encrypted free text. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all(coding.exists() or text.exists())}ereferral-inv-contained-patient-birthdate-encrypted:The birthDate of the contained Patient must not be sent in clear text and must be represented only by the encrypted be-ext-pseudonymized-content extension. {contained.ofType(Patient).all(birthDate.hasValue().not() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists())}ereferral-inv-contained-patient-gender-at-birth-encrypted:The contained Patient genderAtBirth must always be coded as 'other' and must be accompanied by the be-ext-pseudonymized-content encryption extension. {contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').all(value.ofType(CodeableConcept).coding.where(system = 'http://hl7.org/fhir/administrative-gender' and code = 'other').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists()) and contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -689,7 +689,7 @@
     <t>feedback</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-feedback-to-prescriber}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-feedback-to-prescriber}
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
     <t>validity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-validity-period}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-validity-period}
 </t>
   </si>
   <si>
@@ -725,7 +725,7 @@
     <t>latest</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-latest-end-date}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-latest-end-date}
 </t>
   </si>
   <si>
@@ -741,7 +741,7 @@
     <t>performerType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-performer-type}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-performer-type}
 </t>
   </si>
   <si>
@@ -751,7 +751,7 @@
     <t>statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {request-statusReason|5.3.0}
+    <t xml:space="preserve">Extension {request-statusReason|5.4.0}
 </t>
   </si>
   <si>
@@ -819,7 +819,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-prescription-status-reason</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-prescription-status-reason</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -918,7 +918,7 @@
     <t>urgencyJustification</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification}
 </t>
   </si>
   <si>
@@ -934,7 +934,7 @@
     <t>pssInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-pss-info}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-pss-info}
 </t>
   </si>
   <si>
@@ -1097,7 +1097,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1220,7 +1220,7 @@
     <t>ServiceRequest.identifier:SHORT.system</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep-short</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep-short</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:SHORT.value</t>
@@ -1397,7 +1397,7 @@
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-request-intent.html).</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-request-intent.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
@@ -1458,7 +1458,7 @@
     <t>Category that identifies the type of referral (e.g., nursing, physiotherapy)</t>
   </si>
   <si>
-    <t>Categories of care that can be prescribed. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-categories-of-care.html).</t>
+    <t>Categories of care that can be prescribed. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-categories-of-care.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-categories-of-care</t>
@@ -1695,7 +1695,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Technical types of prescriptions for routing and workflow. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-prescription-type.html).</t>
+    <t>Technical types of prescriptions for routing and workflow. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-prescription-type.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-prescription-type</t>
@@ -1749,7 +1749,7 @@
     <t>Care setting track (inpatient, ambulatory, urgency)</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-request-track</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-request-track</t>
   </si>
   <si>
     <t>ServiceRequest.category:track.id</t>
@@ -1800,7 +1800,7 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-imaging-priority</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-imaging-priority</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -2329,7 +2329,7 @@
     <t>To represent information about how the services are to be delivered use the `instructions` element.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension('https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role').value}
+    <t xml:space="preserve">value:extension('https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role').value}
 </t>
   </si>
   <si>
@@ -2376,7 +2376,7 @@
     <t>role</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role|3.0.0}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role|3.0.0}
 </t>
   </si>
   <si>
@@ -2398,7 +2398,7 @@
     <t>ServiceRequest.supportingInfo.extension.url</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:priorResults.extension:role.value[x]</t>
@@ -2527,7 +2527,7 @@
     <t>priorRequestCodeableConcept</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept|3.0.0}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept|3.0.0}
 </t>
   </si>
   <si>
@@ -2543,13 +2543,13 @@
     <t>ServiceRequest.supportingInfo:priorRequest.extension:priorRequestCodeableConcept.url</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:priorRequest.extension:priorRequestCodeableConcept.value[x]</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-imaging-modality</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-imaging-modality</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:priorRequest.extension:role</t>
@@ -2733,7 +2733,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ereferral-inv-patient-condition-strict:A patient condition must contain either free text, or exactly one coding from the allowed ValueSet. Text may accompany a coding. {supportingInfo.where(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role').value = 'patient-condition').extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all((text.exists() and coding.empty()) or (text.empty() and coding.count() = 1 and memberOf('https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/ereferral-vs-imaging-patient-condition-indication')))}</t>
+ereferral-inv-patient-condition-strict:A patient condition must contain either free text, or exactly one coding from the allowed ValueSet. Text may accompany a coding. {supportingInfo.where(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role').value = 'patient-condition').extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all((text.exists() and coding.empty()) or (text.empty() and coding.count() = 1 and memberOf('https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/ereferral-vs-imaging-patient-condition-indication')))}</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:patientCondition.extension:role</t>
@@ -3354,10 +3354,10 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="176.984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="167.85546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="91.13671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="106.58203125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="103.3984375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="62.61328125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-diagnosticimaging.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
